--- a/Def.xlsx
+++ b/Def.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44863FAC-8973-4EDC-A04C-FA20FF6416DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F62315-D5D7-4374-9270-8016D88FFBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1812,35 +1812,86 @@
         </row>
         <row r="89">
           <cell r="AG89" t="str">
-            <v/>
+            <v>鴨嘴炎獸</v>
           </cell>
           <cell r="AH89" t="str">
-            <v/>
+            <v>火</v>
           </cell>
           <cell r="AI89" t="str">
-            <v/>
-          </cell>
-          <cell r="AJ89" t="str">
-            <v/>
-          </cell>
-          <cell r="AK89" t="str">
-            <v/>
+            <v>無</v>
+          </cell>
+          <cell r="AJ89">
+            <v>22.792000000000002</v>
+          </cell>
+          <cell r="AK89">
+            <v>49.432000000000002</v>
           </cell>
         </row>
         <row r="90">
           <cell r="AG90" t="str">
+            <v>超甲狂犀</v>
+          </cell>
+          <cell r="AH90" t="str">
+            <v>地面</v>
+          </cell>
+          <cell r="AI90" t="str">
+            <v>岩石</v>
+          </cell>
+          <cell r="AJ90">
+            <v>34.020000000000003</v>
+          </cell>
+          <cell r="AK90">
+            <v>63.18</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="AG91" t="str">
+            <v>帝牙盧卡</v>
+          </cell>
+          <cell r="AH91" t="str">
+            <v>鋼</v>
+          </cell>
+          <cell r="AI91" t="str">
+            <v>龍</v>
+          </cell>
+          <cell r="AJ91">
+            <v>32.869999999999997</v>
+          </cell>
+          <cell r="AK91">
+            <v>67.069999999999993</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="AG92" t="str">
+            <v>帕路奇亞</v>
+          </cell>
+          <cell r="AH92" t="str">
+            <v>水</v>
+          </cell>
+          <cell r="AI92" t="str">
+            <v>龍</v>
+          </cell>
+          <cell r="AJ92">
+            <v>29.302</v>
+          </cell>
+          <cell r="AK92">
+            <v>62.061999999999998</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="AG93" t="str">
             <v/>
           </cell>
-          <cell r="AH90" t="str">
+          <cell r="AH93" t="str">
             <v/>
           </cell>
-          <cell r="AI90" t="str">
+          <cell r="AI93" t="str">
             <v/>
           </cell>
-          <cell r="AJ90" t="str">
+          <cell r="AJ93" t="str">
             <v/>
           </cell>
-          <cell r="AK90" t="str">
+          <cell r="AK93" t="str">
             <v/>
           </cell>
         </row>
@@ -5244,89 +5295,89 @@
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="str">
         <f>IF([1]攻守數據!AG89 = "", "", [1]攻守數據!AG89)</f>
-        <v/>
+        <v>鴨嘴炎獸</v>
       </c>
       <c r="B88" s="14" t="str">
         <f>IF([1]攻守數據!AH89 = "", "", [1]攻守數據!AH89)</f>
-        <v/>
+        <v>火</v>
       </c>
       <c r="C88" s="14" t="str">
         <f>IF([1]攻守數據!AI89 = "", "", [1]攻守數據!AI89)</f>
-        <v/>
-      </c>
-      <c r="D88" s="15" t="str">
+        <v>無</v>
+      </c>
+      <c r="D88" s="15">
         <f>IF([1]攻守數據!AJ89 = "", "", [1]攻守數據!AJ89)</f>
-        <v/>
-      </c>
-      <c r="E88" s="15" t="str">
+        <v>22.792000000000002</v>
+      </c>
+      <c r="E88" s="15">
         <f>IF([1]攻守數據!AK89 = "", "", [1]攻守數據!AK89)</f>
-        <v/>
+        <v>49.432000000000002</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="str">
         <f>IF([1]攻守數據!AG90 = "", "", [1]攻守數據!AG90)</f>
-        <v/>
+        <v>超甲狂犀</v>
       </c>
       <c r="B89" s="14" t="str">
         <f>IF([1]攻守數據!AH90 = "", "", [1]攻守數據!AH90)</f>
-        <v/>
+        <v>地面</v>
       </c>
       <c r="C89" s="14" t="str">
         <f>IF([1]攻守數據!AI90 = "", "", [1]攻守數據!AI90)</f>
-        <v/>
-      </c>
-      <c r="D89" s="15" t="str">
+        <v>岩石</v>
+      </c>
+      <c r="D89" s="15">
         <f>IF([1]攻守數據!AJ90 = "", "", [1]攻守數據!AJ90)</f>
-        <v/>
-      </c>
-      <c r="E89" s="15" t="str">
+        <v>34.020000000000003</v>
+      </c>
+      <c r="E89" s="15">
         <f>IF([1]攻守數據!AK90 = "", "", [1]攻守數據!AK90)</f>
-        <v/>
+        <v>63.18</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="str">
         <f>IF([1]攻守數據!AG91 = "", "", [1]攻守數據!AG91)</f>
-        <v/>
+        <v>帝牙盧卡</v>
       </c>
       <c r="B90" s="14" t="str">
         <f>IF([1]攻守數據!AH91 = "", "", [1]攻守數據!AH91)</f>
-        <v/>
+        <v>鋼</v>
       </c>
       <c r="C90" s="14" t="str">
         <f>IF([1]攻守數據!AI91 = "", "", [1]攻守數據!AI91)</f>
-        <v/>
-      </c>
-      <c r="D90" s="15" t="str">
+        <v>龍</v>
+      </c>
+      <c r="D90" s="15">
         <f>IF([1]攻守數據!AJ91 = "", "", [1]攻守數據!AJ91)</f>
-        <v/>
-      </c>
-      <c r="E90" s="15" t="str">
+        <v>32.869999999999997</v>
+      </c>
+      <c r="E90" s="15">
         <f>IF([1]攻守數據!AK91 = "", "", [1]攻守數據!AK91)</f>
-        <v/>
+        <v>67.069999999999993</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="str">
         <f>IF([1]攻守數據!AG92 = "", "", [1]攻守數據!AG92)</f>
-        <v/>
+        <v>帕路奇亞</v>
       </c>
       <c r="B91" s="14" t="str">
         <f>IF([1]攻守數據!AH92 = "", "", [1]攻守數據!AH92)</f>
-        <v/>
+        <v>水</v>
       </c>
       <c r="C91" s="14" t="str">
         <f>IF([1]攻守數據!AI92 = "", "", [1]攻守數據!AI92)</f>
-        <v/>
-      </c>
-      <c r="D91" s="15" t="str">
+        <v>龍</v>
+      </c>
+      <c r="D91" s="15">
         <f>IF([1]攻守數據!AJ92 = "", "", [1]攻守數據!AJ92)</f>
-        <v/>
-      </c>
-      <c r="E91" s="15" t="str">
+        <v>29.302</v>
+      </c>
+      <c r="E91" s="15">
         <f>IF([1]攻守數據!AK92 = "", "", [1]攻守數據!AK92)</f>
-        <v/>
+        <v>62.061999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">

--- a/Def.xlsx
+++ b/Def.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F62315-D5D7-4374-9270-8016D88FFBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC45FDF5-4ED2-407F-9AE1-B77ACDA01AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1880,18 +1880,171 @@
         </row>
         <row r="93">
           <cell r="AG93" t="str">
+            <v>瑪狃拉</v>
+          </cell>
+          <cell r="AH93" t="str">
+            <v>冰</v>
+          </cell>
+          <cell r="AI93" t="str">
+            <v>惡</v>
+          </cell>
+          <cell r="AJ93">
+            <v>21.609000000000002</v>
+          </cell>
+          <cell r="AK93">
+            <v>48.069000000000003</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="AG94" t="str">
+            <v>焚焰蚣</v>
+          </cell>
+          <cell r="AH94" t="str">
+            <v>火</v>
+          </cell>
+          <cell r="AI94" t="str">
+            <v>蟲</v>
+          </cell>
+          <cell r="AJ94">
+            <v>25.704000000000001</v>
+          </cell>
+          <cell r="AK94">
+            <v>50.183999999999997</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="AG95" t="str">
+            <v>由克希</v>
+          </cell>
+          <cell r="AH95" t="str">
+            <v>超能力</v>
+          </cell>
+          <cell r="AI95" t="str">
+            <v>無</v>
+          </cell>
+          <cell r="AJ95">
+            <v>34.65</v>
+          </cell>
+          <cell r="AK95">
+            <v>75.150000000000006</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="AG96" t="str">
+            <v>艾姆利多</v>
+          </cell>
+          <cell r="AH96" t="str">
+            <v>超能力</v>
+          </cell>
+          <cell r="AI96" t="str">
+            <v>無</v>
+          </cell>
+          <cell r="AJ96">
+            <v>28.998000000000001</v>
+          </cell>
+          <cell r="AK96">
+            <v>61.218000000000004</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="AG97" t="str">
+            <v>亞克諾姆</v>
+          </cell>
+          <cell r="AH97" t="str">
+            <v>超能力</v>
+          </cell>
+          <cell r="AI97" t="str">
+            <v>無</v>
+          </cell>
+          <cell r="AJ97">
+            <v>20.173999999999999</v>
+          </cell>
+          <cell r="AK97">
+            <v>43.753999999999998</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="AG98" t="str">
             <v/>
           </cell>
-          <cell r="AH93" t="str">
+          <cell r="AH98" t="str">
             <v/>
           </cell>
-          <cell r="AI93" t="str">
+          <cell r="AI98" t="str">
             <v/>
           </cell>
-          <cell r="AJ93" t="str">
+          <cell r="AJ98" t="str">
             <v/>
           </cell>
-          <cell r="AK93" t="str">
+          <cell r="AK98" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="AG99" t="str">
+            <v/>
+          </cell>
+          <cell r="AH99" t="str">
+            <v/>
+          </cell>
+          <cell r="AI99" t="str">
+            <v/>
+          </cell>
+          <cell r="AJ99" t="str">
+            <v/>
+          </cell>
+          <cell r="AK99" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="AG100" t="str">
+            <v/>
+          </cell>
+          <cell r="AH100" t="str">
+            <v/>
+          </cell>
+          <cell r="AI100" t="str">
+            <v/>
+          </cell>
+          <cell r="AJ100" t="str">
+            <v/>
+          </cell>
+          <cell r="AK100" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="AG101" t="str">
+            <v/>
+          </cell>
+          <cell r="AH101" t="str">
+            <v/>
+          </cell>
+          <cell r="AI101" t="str">
+            <v/>
+          </cell>
+          <cell r="AJ101" t="str">
+            <v/>
+          </cell>
+          <cell r="AK101" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="AG102" t="str">
+            <v/>
+          </cell>
+          <cell r="AH102" t="str">
+            <v/>
+          </cell>
+          <cell r="AI102" t="str">
+            <v/>
+          </cell>
+          <cell r="AJ102" t="str">
+            <v/>
+          </cell>
+          <cell r="AK102" t="str">
             <v/>
           </cell>
         </row>
@@ -5383,111 +5536,111 @@
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="14" t="str">
         <f>IF([1]攻守數據!AG93 = "", "", [1]攻守數據!AG93)</f>
-        <v/>
+        <v>瑪狃拉</v>
       </c>
       <c r="B92" s="14" t="str">
         <f>IF([1]攻守數據!AH93 = "", "", [1]攻守數據!AH93)</f>
-        <v/>
+        <v>冰</v>
       </c>
       <c r="C92" s="14" t="str">
         <f>IF([1]攻守數據!AI93 = "", "", [1]攻守數據!AI93)</f>
-        <v/>
-      </c>
-      <c r="D92" s="15" t="str">
+        <v>惡</v>
+      </c>
+      <c r="D92" s="15">
         <f>IF([1]攻守數據!AJ93 = "", "", [1]攻守數據!AJ93)</f>
-        <v/>
-      </c>
-      <c r="E92" s="15" t="str">
+        <v>21.609000000000002</v>
+      </c>
+      <c r="E92" s="15">
         <f>IF([1]攻守數據!AK93 = "", "", [1]攻守數據!AK93)</f>
-        <v/>
+        <v>48.069000000000003</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="14" t="str">
         <f>IF([1]攻守數據!AG94 = "", "", [1]攻守數據!AG94)</f>
-        <v/>
+        <v>焚焰蚣</v>
       </c>
       <c r="B93" s="14" t="str">
         <f>IF([1]攻守數據!AH94 = "", "", [1]攻守數據!AH94)</f>
-        <v/>
+        <v>火</v>
       </c>
       <c r="C93" s="14" t="str">
         <f>IF([1]攻守數據!AI94 = "", "", [1]攻守數據!AI94)</f>
-        <v/>
-      </c>
-      <c r="D93" s="15" t="str">
+        <v>蟲</v>
+      </c>
+      <c r="D93" s="15">
         <f>IF([1]攻守數據!AJ94 = "", "", [1]攻守數據!AJ94)</f>
-        <v/>
-      </c>
-      <c r="E93" s="15" t="str">
+        <v>25.704000000000001</v>
+      </c>
+      <c r="E93" s="15">
         <f>IF([1]攻守數據!AK94 = "", "", [1]攻守數據!AK94)</f>
-        <v/>
+        <v>50.183999999999997</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="str">
         <f>IF([1]攻守數據!AG95 = "", "", [1]攻守數據!AG95)</f>
-        <v/>
+        <v>由克希</v>
       </c>
       <c r="B94" s="14" t="str">
         <f>IF([1]攻守數據!AH95 = "", "", [1]攻守數據!AH95)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="C94" s="14" t="str">
         <f>IF([1]攻守數據!AI95 = "", "", [1]攻守數據!AI95)</f>
-        <v/>
-      </c>
-      <c r="D94" s="15" t="str">
+        <v>無</v>
+      </c>
+      <c r="D94" s="15">
         <f>IF([1]攻守數據!AJ95 = "", "", [1]攻守數據!AJ95)</f>
-        <v/>
-      </c>
-      <c r="E94" s="15" t="str">
+        <v>34.65</v>
+      </c>
+      <c r="E94" s="15">
         <f>IF([1]攻守數據!AK95 = "", "", [1]攻守數據!AK95)</f>
-        <v/>
+        <v>75.150000000000006</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="14" t="str">
         <f>IF([1]攻守數據!AG96 = "", "", [1]攻守數據!AG96)</f>
-        <v/>
+        <v>艾姆利多</v>
       </c>
       <c r="B95" s="14" t="str">
         <f>IF([1]攻守數據!AH96 = "", "", [1]攻守數據!AH96)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="C95" s="14" t="str">
         <f>IF([1]攻守數據!AI96 = "", "", [1]攻守數據!AI96)</f>
-        <v/>
-      </c>
-      <c r="D95" s="15" t="str">
+        <v>無</v>
+      </c>
+      <c r="D95" s="15">
         <f>IF([1]攻守數據!AJ96 = "", "", [1]攻守數據!AJ96)</f>
-        <v/>
-      </c>
-      <c r="E95" s="15" t="str">
+        <v>28.998000000000001</v>
+      </c>
+      <c r="E95" s="15">
         <f>IF([1]攻守數據!AK96 = "", "", [1]攻守數據!AK96)</f>
-        <v/>
+        <v>61.218000000000004</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="str">
         <f>IF([1]攻守數據!AG97 = "", "", [1]攻守數據!AG97)</f>
-        <v/>
+        <v>亞克諾姆</v>
       </c>
       <c r="B96" s="14" t="str">
         <f>IF([1]攻守數據!AH97 = "", "", [1]攻守數據!AH97)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="C96" s="14" t="str">
         <f>IF([1]攻守數據!AI97 = "", "", [1]攻守數據!AI97)</f>
-        <v/>
-      </c>
-      <c r="D96" s="15" t="str">
+        <v>無</v>
+      </c>
+      <c r="D96" s="15">
         <f>IF([1]攻守數據!AJ97 = "", "", [1]攻守數據!AJ97)</f>
-        <v/>
-      </c>
-      <c r="E96" s="15" t="str">
+        <v>20.173999999999999</v>
+      </c>
+      <c r="E96" s="15">
         <f>IF([1]攻守數據!AK97 = "", "", [1]攻守數據!AK97)</f>
-        <v/>
+        <v>43.753999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">

--- a/Def.xlsx
+++ b/Def.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\100.127.78.90\Elton\備分\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC45FDF5-4ED2-407F-9AE1-B77ACDA01AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CACA6E3-E55D-47CA-9398-1EC28F0AD228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2323,7 +2323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z150"/>
-  <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="13"/>
@@ -2413,7 +2413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="str">
         <f>[1]攻守數據!AG3</f>
         <v>幸福蛋</v>
@@ -2577,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="str">
         <f>[1]攻守數據!AG5</f>
         <v>卡比獸</v>
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="str">
         <f>[1]攻守數據!AG9</f>
         <v>拉普拉斯</v>
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="str">
         <f>[1]攻守數據!AG10</f>
         <v>拉帝亞斯</v>
@@ -3069,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="str">
         <f>[1]攻守數據!AG11</f>
         <v>蒼響</v>
@@ -3151,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="str">
         <f>[1]攻守數據!AG12</f>
         <v>拉帝歐斯</v>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="str">
         <f>[1]攻守數據!AG16</f>
         <v>幾何雪花</v>
@@ -3561,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="str">
         <f>[1]攻守數據!AG17</f>
         <v>藏飽栗鼠</v>
